--- a/outputs/final_consolation_200_excluding_selected.xlsx
+++ b/outputs/final_consolation_200_excluding_selected.xlsx
@@ -23093,12 +23093,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Ravi Kumar</t>
+          <t>Saiful Haizam</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>1558303682</t>
+          <t>537089163</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23121,51 +23121,51 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-04-15 21:55:40 GMT+8</t>
+          <t>2026-03-16 23:30:39 GMT+8</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>2026-04-15 21:57:12 GMT+8</t>
+          <t>2026-03-16 23:34:04 GMT+8</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026-04-15 21:55:20 GMT+8</t>
+          <t>2026-03-16 23:24:24 GMT+8</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-04-15 21:54:41 GMT+8</t>
+          <t>2026-02-20 22:23:49 GMT+8</t>
         </is>
       </c>
       <c r="M199" t="n">
-        <v>35766</v>
+        <v>15579</v>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-04-15 21:57:12 GMT+8</t>
+          <t>2026-03-16 23:30:39 GMT+8</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/share/p/1BMM3FeM3B/</t>
+          <t>Saya berkongsi rezeki dengan membeli Tropicana Twister dan kemudian diagih-agihkan kepada jiran tetangga</t>
         </is>
       </c>
       <c r="P199" t="n">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="Q199" t="n">
-        <v>1.1</v>
+        <v>-2.4</v>
       </c>
       <c r="R199" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="S199" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T199" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U199" t="n">
         <v>0</v>
@@ -23177,13 +23177,13 @@
         <v>0</v>
       </c>
       <c r="X199" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA199" t="n">
         <v>0</v>
@@ -23208,12 +23208,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Saiful Haizam</t>
+          <t>Salmah Jaafar</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>537089163</t>
+          <t>26750312877989179</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23236,48 +23236,48 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-03-16 23:30:39 GMT+8</t>
+          <t>2026-04-12 09:42:11 GMT+8</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>2026-03-16 23:34:04 GMT+8</t>
+          <t>2026-04-12 09:43:52 GMT+8</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-03-16 23:24:24 GMT+8</t>
+          <t>2026-04-12 09:40:28 GMT+8</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-02-20 22:23:49 GMT+8</t>
+          <t>2026-04-12 09:40:28 GMT+8</t>
         </is>
       </c>
       <c r="M200" t="n">
-        <v>15579</v>
+        <v>33096</v>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-03-16 23:30:39 GMT+8</t>
+          <t>2026-04-12 09:43:52 GMT+8</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Saya berkongsi rezeki dengan membeli Tropicana Twister dan kemudian diagih-agihkan kepada jiran tetangga</t>
+          <t>Saya bantu orang menunjukan jalan.</t>
         </is>
       </c>
       <c r="P200" t="n">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="Q200" t="n">
-        <v>-2.4</v>
+        <v>10.85</v>
       </c>
       <c r="R200" t="n">
-        <v>2.6</v>
+        <v>0.85</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T200" t="n">
         <v>5</v>
@@ -23292,10 +23292,10 @@
         <v>0</v>
       </c>
       <c r="X200" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z200" t="n">
         <v>1</v>
@@ -23323,12 +23323,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Salmah Jaafar</t>
+          <t>Sariffudin Fiza</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>26750312877989179</t>
+          <t>25640455475627828</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23351,48 +23351,48 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-04-12 09:42:11 GMT+8</t>
+          <t>2026-04-17 15:40:28 GMT+8</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>2026-04-12 09:43:52 GMT+8</t>
+          <t>2026-04-17 16:13:56 GMT+8</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026-04-12 09:40:28 GMT+8</t>
+          <t>2026-04-17 16:12:47 GMT+8</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-04-12 09:40:28 GMT+8</t>
+          <t>2026-04-17 15:39:37 GMT+8</t>
         </is>
       </c>
       <c r="M201" t="n">
-        <v>33096</v>
+        <v>36502</v>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-04-12 09:43:52 GMT+8</t>
+          <t>2026-04-17 15:40:28 GMT+8</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>Saya bantu orang menunjukan jalan.</t>
+          <t>saya sayang family saya</t>
         </is>
       </c>
       <c r="P201" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="Q201" t="n">
-        <v>10.85</v>
+        <v>-9.43</v>
       </c>
       <c r="R201" t="n">
-        <v>0.85</v>
+        <v>0.575</v>
       </c>
       <c r="S201" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T201" t="n">
         <v>5</v>
@@ -23404,13 +23404,13 @@
         <v>0</v>
       </c>
       <c r="W201" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="X201" t="n">
         <v>0</v>
       </c>
       <c r="Y201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z201" t="n">
         <v>1</v>
@@ -23422,7 +23422,7 @@
         <v>0</v>
       </c>
       <c r="AC201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD201" t="inlineStr">
         <is>

--- a/outputs/final_consolation_200_excluding_selected.xlsx
+++ b/outputs/final_consolation_200_excluding_selected.xlsx
@@ -17113,12 +17113,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ashley WS</t>
+          <t>Aziana Nazri</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>26128720686781725</t>
+          <t>26592970736982414</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -17141,48 +17141,48 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-03-05 10:47:53 GMT+8</t>
+          <t>2026-04-11 07:54:31 GMT+8</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>2026-03-05 13:46:37 GMT+8</t>
+          <t>2026-04-11 07:55:08 GMT+8</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-03-05 10:33:35 GMT+8</t>
+          <t>2026-04-11 07:53:44 GMT+8</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-03-05 10:33:34 GMT+8</t>
+          <t>2026-04-11 07:53:05 GMT+8</t>
         </is>
       </c>
       <c r="M147" t="n">
-        <v>5671</v>
+        <v>32380</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-03-05 10:47:53 GMT+8</t>
+          <t>2026-04-11 07:55:08 GMT+8</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>test test test test test test</t>
+          <t>Saya suka belanja keluarga dengan tropicana</t>
         </is>
       </c>
       <c r="P147" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Q147" t="n">
-        <v>0.72</v>
+        <v>-13.92</v>
       </c>
       <c r="R147" t="n">
-        <v>0.725</v>
+        <v>1.075</v>
       </c>
       <c r="S147" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T147" t="n">
         <v>0</v>
@@ -17194,13 +17194,13 @@
         <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="X147" t="n">
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z147" t="n">
         <v>0</v>
@@ -17212,7 +17212,7 @@
         <v>0</v>
       </c>
       <c r="AC147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD147" t="inlineStr">
         <is>
@@ -17228,12 +17228,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Aziana Nazri</t>
+          <t>Azi Mah</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>26592970736982414</t>
+          <t>25925220943818297</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -17256,51 +17256,51 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-04-11 07:54:31 GMT+8</t>
+          <t>2026-04-17 14:53:22 GMT+8</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>2026-04-11 07:55:08 GMT+8</t>
+          <t>2026-04-17 14:55:24 GMT+8</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-04-11 07:53:44 GMT+8</t>
+          <t>2026-04-17 14:52:28 GMT+8</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-04-11 07:53:05 GMT+8</t>
+          <t>2026-04-17 14:52:27 GMT+8</t>
         </is>
       </c>
       <c r="M148" t="n">
-        <v>32380</v>
+        <v>36386</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-04-11 07:55:08 GMT+8</t>
+          <t>2026-04-17 14:55:24 GMT+8</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Saya suka belanja keluarga dengan tropicana</t>
+          <t>Saya datang rumah terbukak, saya kongsi Tropicana twister</t>
         </is>
       </c>
       <c r="P148" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="Q148" t="n">
-        <v>-13.92</v>
+        <v>-8.57</v>
       </c>
       <c r="R148" t="n">
-        <v>1.075</v>
+        <v>1.425</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T148" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -17309,16 +17309,16 @@
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X148" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA148" t="n">
         <v>0</v>
@@ -17327,7 +17327,7 @@
         <v>0</v>
       </c>
       <c r="AC148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD148" t="inlineStr">
         <is>
@@ -17343,12 +17343,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Azi Mah</t>
+          <t>Azli Abd Rahim</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>25925220943818297</t>
+          <t>34881210441524280</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -17371,48 +17371,48 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-04-17 14:53:22 GMT+8</t>
+          <t>2026-04-11 09:35:04 GMT+8</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>2026-04-17 14:55:24 GMT+8</t>
+          <t>2026-04-11 09:36:20 GMT+8</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-04-17 14:52:28 GMT+8</t>
+          <t>2026-04-11 09:33:48 GMT+8</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-04-17 14:52:27 GMT+8</t>
+          <t>2026-04-11 09:33:48 GMT+8</t>
         </is>
       </c>
       <c r="M149" t="n">
-        <v>36386</v>
+        <v>32540</v>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-04-17 14:55:24 GMT+8</t>
+          <t>2026-04-11 09:36:20 GMT+8</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Saya datang rumah terbukak, saya kongsi Tropicana twister</t>
+          <t>saya bantu jiran sebelah rumah siram pokok bunga dan sapu sampah depan rumah @ bagi makan kucing</t>
         </is>
       </c>
       <c r="P149" t="n">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="Q149" t="n">
-        <v>-8.57</v>
+        <v>17.4</v>
       </c>
       <c r="R149" t="n">
-        <v>1.425</v>
+        <v>2.4</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T149" t="n">
         <v>5</v>
@@ -17427,10 +17427,10 @@
         <v>0</v>
       </c>
       <c r="X149" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z149" t="n">
         <v>1</v>
@@ -17458,12 +17458,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Azli Abd Rahim</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>34881210441524280</t>
+          <t>318059585</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -17486,52 +17486,52 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-04-11 09:35:04 GMT+8</t>
+          <t>2026-02-24 18:36:40 GMT+8</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>2026-04-11 09:36:20 GMT+8</t>
+          <t>2026-02-24 18:39:37 GMT+8</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-04-11 09:33:48 GMT+8</t>
+          <t>2026-02-24 18:35:16 GMT+8</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-04-11 09:33:48 GMT+8</t>
+          <t>2026-02-18 18:01:56 GMT+8</t>
         </is>
       </c>
       <c r="M150" t="n">
-        <v>32540</v>
+        <v>638</v>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-04-11 09:36:20 GMT+8</t>
+          <t>2026-02-24 18:36:40 GMT+8</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>saya bantu jiran sebelah rumah siram pokok bunga dan sapu sampah depan rumah @ bagi makan kucing</t>
+          <t>Saya kongsi kebaikan Tropicana Twister bersama rakan sekerja dan keluarga</t>
         </is>
       </c>
       <c r="P150" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="Q150" t="n">
-        <v>17.4</v>
+        <v>6.82</v>
       </c>
       <c r="R150" t="n">
-        <v>2.4</v>
+        <v>1.825</v>
       </c>
       <c r="S150" t="n">
+        <v>15</v>
+      </c>
+      <c r="T150" t="n">
         <v>10</v>
       </c>
-      <c r="T150" t="n">
-        <v>5</v>
-      </c>
       <c r="U150" t="n">
         <v>0</v>
       </c>
@@ -17542,13 +17542,13 @@
         <v>0</v>
       </c>
       <c r="X150" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA150" t="n">
         <v>0</v>
@@ -17573,12 +17573,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Ct Ayu</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>318059585</t>
+          <t>27061818516739837</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -17601,51 +17601,51 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-02-24 18:36:40 GMT+8</t>
+          <t>2026-03-14 23:04:03 GMT+8</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>2026-02-24 18:39:37 GMT+8</t>
+          <t>2026-03-14 23:07:43 GMT+8</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-02-24 18:35:16 GMT+8</t>
+          <t>2026-03-14 23:02:09 GMT+8</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-02-18 18:01:56 GMT+8</t>
+          <t>2026-03-14 23:02:08 GMT+8</t>
         </is>
       </c>
       <c r="M151" t="n">
-        <v>638</v>
+        <v>13048</v>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-02-24 18:36:40 GMT+8</t>
+          <t>2026-03-14 23:07:43 GMT+8</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Saya kongsi kebaikan Tropicana Twister bersama rakan sekerja dan keluarga</t>
+          <t>saya bantu jiran buang sampah</t>
         </is>
       </c>
       <c r="P151" t="n">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="Q151" t="n">
-        <v>6.82</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="R151" t="n">
-        <v>1.825</v>
+        <v>0.725</v>
       </c>
       <c r="S151" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T151" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U151" t="n">
         <v>0</v>
@@ -17654,16 +17654,16 @@
         <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="X151" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA151" t="n">
         <v>0</v>
@@ -17672,7 +17672,7 @@
         <v>0</v>
       </c>
       <c r="AC151" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD151" t="inlineStr">
         <is>
@@ -17688,12 +17688,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ct Ayu</t>
+          <t>Ezhar Sam</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>27061818516739837</t>
+          <t>1582613290</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -17716,48 +17716,48 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-03-14 23:04:03 GMT+8</t>
+          <t>2026-03-13 19:09:28 GMT+8</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>2026-03-14 23:07:43 GMT+8</t>
+          <t>2026-03-13 19:11:04 GMT+8</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-03-14 23:02:09 GMT+8</t>
+          <t>2026-03-13 19:06:56 GMT+8</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-03-14 23:02:08 GMT+8</t>
+          <t>2026-02-16 15:23:37 GMT+8</t>
         </is>
       </c>
       <c r="M152" t="n">
-        <v>13048</v>
+        <v>11490</v>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-03-14 23:07:43 GMT+8</t>
+          <t>2026-03-13 19:09:28 GMT+8</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>saya bantu jiran buang sampah</t>
+          <t>Saya bantu seorang penunggang motosikal menolak motornya hingga ke stesen minyak kira-kira 6km kerana beliau kehabisan minyak.</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="Q152" t="n">
-        <v>-9.279999999999999</v>
+        <v>13.15</v>
       </c>
       <c r="R152" t="n">
-        <v>0.725</v>
+        <v>3.15</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T152" t="n">
         <v>5</v>
@@ -17769,13 +17769,13 @@
         <v>0</v>
       </c>
       <c r="W152" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X152" t="n">
         <v>0</v>
       </c>
       <c r="Y152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z152" t="n">
         <v>1</v>
@@ -17787,7 +17787,7 @@
         <v>0</v>
       </c>
       <c r="AC152" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD152" t="inlineStr">
         <is>
@@ -17803,12 +17803,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ezhar Sam</t>
+          <t>Fairous BI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1582613290</t>
+          <t>26978487381734820</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -17831,48 +17831,48 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-03-13 19:09:28 GMT+8</t>
+          <t>2026-04-12 06:47:00 GMT+8</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>2026-03-13 19:11:04 GMT+8</t>
+          <t>2026-04-12 08:16:11 GMT+8</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-03-13 19:06:56 GMT+8</t>
+          <t>2026-04-12 08:15:03 GMT+8</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-02-16 15:23:37 GMT+8</t>
+          <t>2026-04-12 06:45:59 GMT+8</t>
         </is>
       </c>
       <c r="M153" t="n">
-        <v>11490</v>
+        <v>32845</v>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-03-13 19:09:28 GMT+8</t>
+          <t>2026-04-12 08:16:11 GMT+8</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Saya bantu seorang penunggang motosikal menolak motornya hingga ke stesen minyak kira-kira 6km kerana beliau kehabisan minyak.</t>
+          <t>Saya membantu isteri saya menjaga anak</t>
         </is>
       </c>
       <c r="P153" t="n">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="Q153" t="n">
-        <v>13.15</v>
+        <v>20.95</v>
       </c>
       <c r="R153" t="n">
-        <v>3.15</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="S153" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T153" t="n">
         <v>5</v>
@@ -17890,7 +17890,7 @@
         <v>0</v>
       </c>
       <c r="Y153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z153" t="n">
         <v>1</v>
@@ -17918,12 +17918,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Fairous BI</t>
+          <t>Fendi Zainuddin</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>26978487381734820</t>
+          <t>26717952801155266</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -17946,51 +17946,51 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-04-12 06:47:00 GMT+8</t>
+          <t>2026-04-17 15:07:45 GMT+8</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>2026-04-12 08:16:11 GMT+8</t>
+          <t>2026-04-17 15:08:42 GMT+8</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-04-12 08:15:03 GMT+8</t>
+          <t>2026-04-17 15:06:50 GMT+8</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-04-12 06:45:59 GMT+8</t>
+          <t>2026-04-17 15:06:49 GMT+8</t>
         </is>
       </c>
       <c r="M154" t="n">
-        <v>32845</v>
+        <v>36418</v>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-04-12 08:16:11 GMT+8</t>
+          <t>2026-04-17 15:08:42 GMT+8</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Saya membantu isteri saya menjaga anak</t>
+          <t>Saya suka belanja kawan makan</t>
         </is>
       </c>
       <c r="P154" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Q154" t="n">
-        <v>20.95</v>
+        <v>-14.28</v>
       </c>
       <c r="R154" t="n">
-        <v>0.9500000000000001</v>
+        <v>0.725</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T154" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -17999,16 +17999,16 @@
         <v>0</v>
       </c>
       <c r="W154" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="X154" t="n">
         <v>0</v>
       </c>
       <c r="Y154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA154" t="n">
         <v>0</v>
@@ -18017,7 +18017,7 @@
         <v>0</v>
       </c>
       <c r="AC154" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD154" t="inlineStr">
         <is>
@@ -18033,12 +18033,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Fatah Burhan</t>
+          <t>Fezy Lah Deen</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>26765561226434605</t>
+          <t>27642021585386706</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -18061,45 +18061,45 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-04-17 14:51:15 GMT+8</t>
+          <t>2026-04-12 08:47:41 GMT+8</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2026-04-17 17:54:35 GMT+8</t>
+          <t>2026-04-12 08:50:55 GMT+8</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-04-17 17:53:53 GMT+8</t>
+          <t>2026-04-12 08:46:44 GMT+8</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-04-17 14:47:03 GMT+8</t>
+          <t>2026-04-12 08:44:56 GMT+8</t>
         </is>
       </c>
       <c r="M155" t="n">
-        <v>36360</v>
+        <v>32947</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-04-17 14:51:15 GMT+8</t>
+          <t>2026-04-12 08:50:55 GMT+8</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Saya suka buat aktiviti beriadah bersama keluarga</t>
+          <t>Saya suka belanja family makan Dan Jln2</t>
         </is>
       </c>
       <c r="P155" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="Q155" t="n">
-        <v>11.22</v>
+        <v>10.98</v>
       </c>
       <c r="R155" t="n">
-        <v>1.225</v>
+        <v>0.9750000000000001</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18148,12 +18148,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Fatini Hasnol</t>
+          <t>Fieyza Peace</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>26039702679034991</t>
+          <t>1864364624</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -18176,45 +18176,45 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-04-01 16:44:19 GMT+8</t>
+          <t>2026-04-04 08:36:24 GMT+8</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>2026-04-01 16:45:12 GMT+8</t>
+          <t>2026-04-04 08:37:46 GMT+8</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-04-01 16:43:22 GMT+8</t>
+          <t>2026-04-04 08:35:20 GMT+8</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-04-01 16:09:11 GMT+8</t>
+          <t>2026-04-04 08:35:20 GMT+8</t>
         </is>
       </c>
       <c r="M156" t="n">
-        <v>27357</v>
+        <v>29946</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-04-01 16:44:19 GMT+8</t>
+          <t>2026-04-04 08:37:46 GMT+8</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Saya suka tolong orang tua lintas jalan</t>
+          <t>Sy suka membantu jiran berniaga</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="Q156" t="n">
-        <v>10.98</v>
+        <v>10.78</v>
       </c>
       <c r="R156" t="n">
-        <v>0.9750000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -18263,12 +18263,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Fendi Zainuddin</t>
+          <t>Firdaus Hakimi</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>26717952801155266</t>
+          <t>26680069594958068</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -18291,51 +18291,51 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-04-17 15:07:45 GMT+8</t>
+          <t>2026-04-11 09:00:25 GMT+8</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>2026-04-17 15:08:42 GMT+8</t>
+          <t>2026-04-11 09:00:53 GMT+8</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-04-17 15:06:50 GMT+8</t>
+          <t>2026-04-11 08:59:30 GMT+8</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-04-17 15:06:49 GMT+8</t>
+          <t>2026-04-11 08:59:30 GMT+8</t>
         </is>
       </c>
       <c r="M157" t="n">
-        <v>36418</v>
+        <v>32469</v>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-04-17 15:08:42 GMT+8</t>
+          <t>2026-04-11 09:00:53 GMT+8</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Saya suka belanja kawan makan</t>
+          <t>sy suka bantu family sy</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q157" t="n">
-        <v>-14.28</v>
+        <v>10.58</v>
       </c>
       <c r="R157" t="n">
-        <v>0.725</v>
+        <v>0.575</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T157" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U157" t="n">
         <v>0</v>
@@ -18344,16 +18344,16 @@
         <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X157" t="n">
         <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA157" t="n">
         <v>0</v>
@@ -18362,7 +18362,7 @@
         <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AD157" t="inlineStr">
         <is>
@@ -18378,12 +18378,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Fezy Lah Deen</t>
+          <t>Himawar Tintin Rie</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>27642021585386706</t>
+          <t>25901772266190399</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -18406,48 +18406,48 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-04-12 08:47:41 GMT+8</t>
+          <t>2026-03-16 14:50:14 GMT+8</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>2026-04-12 08:50:55 GMT+8</t>
+          <t>2026-03-16 14:52:31 GMT+8</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-04-12 08:46:44 GMT+8</t>
+          <t>2026-03-16 14:03:46 GMT+8</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-04-12 08:44:56 GMT+8</t>
+          <t>2026-03-16 14:03:46 GMT+8</t>
         </is>
       </c>
       <c r="M158" t="n">
-        <v>32947</v>
+        <v>14856</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-04-12 08:50:55 GMT+8</t>
+          <t>2026-03-16 14:50:14 GMT+8</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Saya suka belanja family makan Dan Jln2</t>
+          <t>Membawa stray cat yg sering lepak kat rumah yg cedera parah di kaki untuk rawatan… Kerana dia garang sangat, terpaksa masuk ward supaya doctor boleh rawat (cuci luka dan bagi ubat) harian. Sekarang sudah dekat 2 bulan dan luka semakin kecil tapi masih terbuka (jika discharge, duduk luar as stray, luka akan jadi busuk balik dan tak sembuh)… Ini waktu melawat dia utk hari ini</t>
         </is>
       </c>
       <c r="P158" t="n">
-        <v>39</v>
+        <v>376</v>
       </c>
       <c r="Q158" t="n">
-        <v>10.98</v>
+        <v>13.4</v>
       </c>
       <c r="R158" t="n">
-        <v>0.9750000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T158" t="n">
         <v>0</v>
@@ -18456,7 +18456,7 @@
         <v>0</v>
       </c>
       <c r="V158" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W158" t="n">
         <v>0</v>
@@ -18465,7 +18465,7 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z158" t="n">
         <v>0</v>
@@ -18474,7 +18474,7 @@
         <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC158" t="n">
         <v>1</v>
@@ -18493,12 +18493,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Fieyza Peace</t>
+          <t>Idha Idris</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1864364624</t>
+          <t>26896237420064278</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -18521,51 +18521,51 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-04-04 08:36:24 GMT+8</t>
+          <t>2026-04-17 15:55:12 GMT+8</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>2026-04-04 08:37:46 GMT+8</t>
+          <t>2026-04-17 16:08:51 GMT+8</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-04-04 08:35:20 GMT+8</t>
+          <t>2026-04-17 16:08:08 GMT+8</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-04-04 08:35:20 GMT+8</t>
+          <t>2026-04-17 15:54:20 GMT+8</t>
         </is>
       </c>
       <c r="M159" t="n">
-        <v>29946</v>
+        <v>36572</v>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-04-04 08:37:46 GMT+8</t>
+          <t>2026-04-17 16:08:51 GMT+8</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Sy suka membantu jiran berniaga</t>
+          <t>saya suka makan bersama keluarga</t>
         </is>
       </c>
       <c r="P159" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q159" t="n">
-        <v>10.78</v>
+        <v>-14.2</v>
       </c>
       <c r="R159" t="n">
-        <v>0.775</v>
+        <v>0.8</v>
       </c>
       <c r="S159" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T159" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U159" t="n">
         <v>0</v>
@@ -18574,16 +18574,16 @@
         <v>0</v>
       </c>
       <c r="W159" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="X159" t="n">
         <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA159" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
         <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="AD159" t="inlineStr">
         <is>
@@ -18608,12 +18608,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Firdaus Hakimi</t>
+          <t>Jue Herman</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>26680069594958068</t>
+          <t>856282500</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -18636,48 +18636,48 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-04-11 09:00:25 GMT+8</t>
+          <t>2026-04-07 19:05:48 GMT+8</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>2026-04-11 09:00:53 GMT+8</t>
+          <t>2026-04-07 19:06:24 GMT+8</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-04-11 08:59:30 GMT+8</t>
+          <t>2026-04-07 19:05:15 GMT+8</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-04-11 08:59:30 GMT+8</t>
+          <t>2026-04-07 19:04:43 GMT+8</t>
         </is>
       </c>
       <c r="M160" t="n">
-        <v>32469</v>
+        <v>31157</v>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-04-11 09:00:53 GMT+8</t>
+          <t>2026-04-07 19:05:48 GMT+8</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>sy suka bantu family sy</t>
+          <t>saya tolong mak saya harini</t>
         </is>
       </c>
       <c r="P160" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q160" t="n">
-        <v>10.58</v>
+        <v>15.68</v>
       </c>
       <c r="R160" t="n">
-        <v>0.575</v>
+        <v>0.6749999999999999</v>
       </c>
       <c r="S160" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T160" t="n">
         <v>5</v>
@@ -18695,7 +18695,7 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z160" t="n">
         <v>1</v>
@@ -18723,12 +18723,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Himawar Tintin Rie</t>
+          <t>Kamariah Nor</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>25901772266190399</t>
+          <t>45402747</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -18751,48 +18751,48 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-03-16 14:50:14 GMT+8</t>
+          <t>2026-04-19 13:07:12 GMT+8</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>2026-03-16 14:52:31 GMT+8</t>
+          <t>2026-04-19 13:10:37 GMT+8</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-03-16 14:03:46 GMT+8</t>
+          <t>2026-04-19 13:05:49 GMT+8</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-03-16 14:03:46 GMT+8</t>
+          <t>2026-04-19 13:04:18 GMT+8</t>
         </is>
       </c>
       <c r="M161" t="n">
-        <v>14856</v>
+        <v>36903</v>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-03-16 14:50:14 GMT+8</t>
+          <t>2026-04-19 13:07:12 GMT+8</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Membawa stray cat yg sering lepak kat rumah yg cedera parah di kaki untuk rawatan… Kerana dia garang sangat, terpaksa masuk ward supaya doctor boleh rawat (cuci luka dan bagi ubat) harian. Sekarang sudah dekat 2 bulan dan luka semakin kecil tapi masih terbuka (jika discharge, duduk luar as stray, luka akan jadi busuk balik dan tak sembuh)… Ini waktu melawat dia utk hari ini</t>
+          <t>Saya suka memberi makanan untuk kucing kucing jalanan</t>
         </is>
       </c>
       <c r="P161" t="n">
-        <v>376</v>
+        <v>53</v>
       </c>
       <c r="Q161" t="n">
-        <v>13.4</v>
+        <v>6.32</v>
       </c>
       <c r="R161" t="n">
-        <v>9.4</v>
+        <v>1.325</v>
       </c>
       <c r="S161" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T161" t="n">
         <v>0</v>
@@ -18801,7 +18801,7 @@
         <v>0</v>
       </c>
       <c r="V161" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W161" t="n">
         <v>0</v>
@@ -18810,7 +18810,7 @@
         <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z161" t="n">
         <v>0</v>
@@ -18819,7 +18819,7 @@
         <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
         <v>1</v>
@@ -18838,12 +18838,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Idha Idris</t>
+          <t>Kam Wai Kwan</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>26896237420064278</t>
+          <t>25230176969988610</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -18866,51 +18866,51 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-04-17 15:55:12 GMT+8</t>
+          <t>2026-03-27 18:42:15 GMT+8</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>2026-04-17 16:08:51 GMT+8</t>
+          <t>2026-03-27 18:45:05 GMT+8</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-04-17 16:08:08 GMT+8</t>
+          <t>2026-03-27 18:40:36 GMT+8</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-04-17 15:54:20 GMT+8</t>
+          <t>2026-03-27 18:40:35 GMT+8</t>
         </is>
       </c>
       <c r="M162" t="n">
-        <v>36572</v>
+        <v>23605</v>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-04-17 16:08:51 GMT+8</t>
+          <t>2026-03-27 18:45:05 GMT+8</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>saya suka makan bersama keluarga</t>
+          <t>Saya mahu menolong datuk &amp; nenek memastikan rumah kemas Dan baru</t>
         </is>
       </c>
       <c r="P162" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="Q162" t="n">
-        <v>-14.2</v>
+        <v>21.6</v>
       </c>
       <c r="R162" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T162" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U162" t="n">
         <v>0</v>
@@ -18919,16 +18919,16 @@
         <v>0</v>
       </c>
       <c r="W162" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X162" t="n">
         <v>0</v>
       </c>
       <c r="Y162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA162" t="n">
         <v>0</v>
@@ -18937,7 +18937,7 @@
         <v>0</v>
       </c>
       <c r="AC162" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="AD162" t="inlineStr">
         <is>
@@ -18953,12 +18953,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Jamilah Manon</t>
+          <t>Kavitha Jaganathan</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>35287738957506135</t>
+          <t>25953022347654371</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -18981,45 +18981,45 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-04-17 16:13:20 GMT+8</t>
+          <t>2026-03-14 17:14:06 GMT+8</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>2026-04-17 16:17:32 GMT+8</t>
+          <t>2026-03-14 17:15:34 GMT+8</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-04-17 16:16:12 GMT+8</t>
+          <t>2026-03-14 17:11:46 GMT+8</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-04-17 16:12:26 GMT+8</t>
+          <t>2026-03-14 17:11:14 GMT+8</t>
         </is>
       </c>
       <c r="M163" t="n">
-        <v>36597</v>
+        <v>12816</v>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-04-17 16:17:32 GMT+8</t>
+          <t>2026-03-14 17:15:34 GMT+8</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Saya suka pergi jogging bersama kawan</t>
+          <t>Saya menyumbang 12 botol Topicana Twister kepada rumah anak yatim berhampiran rumah saya</t>
         </is>
       </c>
       <c r="P163" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="Q163" t="n">
-        <v>10.92</v>
+        <v>-7.8</v>
       </c>
       <c r="R163" t="n">
-        <v>0.925</v>
+        <v>2.2</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19037,7 +19037,7 @@
         <v>0</v>
       </c>
       <c r="X163" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y163" t="n">
         <v>2</v>
@@ -19068,12 +19068,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Jue Herman</t>
+          <t>Khawlah Al Azwar</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>856282500</t>
+          <t>26988101557453565</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -19096,51 +19096,51 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-04-07 19:05:48 GMT+8</t>
+          <t>2026-04-11 09:34:12 GMT+8</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>2026-04-07 19:06:24 GMT+8</t>
+          <t>2026-04-11 09:37:06 GMT+8</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-04-07 19:05:15 GMT+8</t>
+          <t>2026-04-11 09:36:16 GMT+8</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-04-07 19:04:43 GMT+8</t>
+          <t>2026-04-11 09:33:10 GMT+8</t>
         </is>
       </c>
       <c r="M164" t="n">
-        <v>31157</v>
+        <v>32535</v>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-04-07 19:05:48 GMT+8</t>
+          <t>2026-04-11 09:34:12 GMT+8</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>saya tolong mak saya harini</t>
+          <t>Sy suka menyeryai run harini...</t>
         </is>
       </c>
       <c r="P164" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Q164" t="n">
-        <v>15.68</v>
+        <v>0.78</v>
       </c>
       <c r="R164" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.775</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T164" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U164" t="n">
         <v>0</v>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA164" t="n">
         <v>0</v>
@@ -19183,12 +19183,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Kamariah Nor</t>
+          <t>Kirtanah Ravintharan</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>45402747</t>
+          <t>26327752256875020</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -19211,51 +19211,51 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-04-19 13:07:12 GMT+8</t>
+          <t>2026-04-12 09:08:22 GMT+8</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>2026-04-19 13:10:37 GMT+8</t>
+          <t>2026-04-12 09:09:16 GMT+8</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-04-19 13:05:49 GMT+8</t>
+          <t>2026-04-12 09:06:03 GMT+8</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-04-19 13:04:18 GMT+8</t>
+          <t>2026-04-12 09:06:03 GMT+8</t>
         </is>
       </c>
       <c r="M165" t="n">
-        <v>36903</v>
+        <v>33014</v>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-04-19 13:07:12 GMT+8</t>
+          <t>2026-04-12 09:09:16 GMT+8</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Saya suka memberi makanan untuk kucing kucing jalanan</t>
+          <t>Hari ini, saya memilih untuk menyebarkan kebaikan dengan membantu jiran mengangkat barang dan berkongsi rezeki dengan rakan. Walaupun kecil, saya percaya setiap kebaikan mampu memberi makna kepada orang lain.</t>
         </is>
       </c>
       <c r="P165" t="n">
-        <v>53</v>
+        <v>208</v>
       </c>
       <c r="Q165" t="n">
-        <v>6.32</v>
+        <v>10.2</v>
       </c>
       <c r="R165" t="n">
-        <v>1.325</v>
+        <v>5.2</v>
       </c>
       <c r="S165" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T165" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U165" t="n">
         <v>0</v>
@@ -19264,16 +19264,16 @@
         <v>0</v>
       </c>
       <c r="W165" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="X165" t="n">
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA165" t="n">
         <v>0</v>
@@ -19282,7 +19282,7 @@
         <v>0</v>
       </c>
       <c r="AC165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD165" t="inlineStr">
         <is>
@@ -19298,12 +19298,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Kam Wai Kwan</t>
+          <t>Lee Pei Ting</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>25230176969988610</t>
+          <t>25465212196488673</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -19326,51 +19326,51 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-03-27 18:42:15 GMT+8</t>
+          <t>2026-04-11 10:00:06 GMT+8</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>2026-03-27 18:45:05 GMT+8</t>
+          <t>2026-04-11 10:00:36 GMT+8</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-03-27 18:40:36 GMT+8</t>
+          <t>2026-04-11 09:59:11 GMT+8</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-03-27 18:40:35 GMT+8</t>
+          <t>2026-04-11 09:59:11 GMT+8</t>
         </is>
       </c>
       <c r="M166" t="n">
-        <v>23605</v>
+        <v>32591</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-03-27 18:45:05 GMT+8</t>
+          <t>2026-04-11 10:00:06 GMT+8</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Saya mahu menolong datuk &amp; nenek memastikan rumah kemas Dan baru</t>
+          <t>Say suka bersukan dengan keluarga dan kawan kawan.</t>
         </is>
       </c>
       <c r="P166" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="Q166" t="n">
-        <v>21.6</v>
+        <v>11.25</v>
       </c>
       <c r="R166" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="S166" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T166" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U166" t="n">
         <v>0</v>
@@ -19385,10 +19385,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA166" t="n">
         <v>0</v>
@@ -19413,12 +19413,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Karan Patel</t>
+          <t>Lukman Haqem</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1826887376</t>
+          <t>26297421923276894</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -19441,51 +19441,51 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-04-13 21:25:26 GMT+8</t>
+          <t>2026-03-15 21:32:54 GMT+8</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>2026-04-13 21:25:45 GMT+8</t>
+          <t>2026-03-15 21:33:49 GMT+8</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-04-13 21:25:01 GMT+8</t>
+          <t>2026-03-15 21:32:09 GMT+8</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-04-13 21:24:25 GMT+8</t>
+          <t>2026-03-15 21:31:38 GMT+8</t>
         </is>
       </c>
       <c r="M167" t="n">
-        <v>33701</v>
+        <v>14126</v>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-04-13 21:25:26 GMT+8</t>
+          <t>2026-03-15 21:32:54 GMT+8</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Saya bantu rakan membawa buku yang banyak ke kelas.</t>
+          <t>Saya cuti untuk family</t>
         </is>
       </c>
       <c r="P167" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="Q167" t="n">
-        <v>-8.73</v>
+        <v>10.55</v>
       </c>
       <c r="R167" t="n">
-        <v>1.275</v>
+        <v>0.55</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
       </c>
       <c r="T167" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U167" t="n">
         <v>0</v>
@@ -19494,7 +19494,7 @@
         <v>0</v>
       </c>
       <c r="W167" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X167" t="n">
         <v>0</v>
@@ -19503,7 +19503,7 @@
         <v>2</v>
       </c>
       <c r="Z167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA167" t="n">
         <v>0</v>
@@ -19512,7 +19512,7 @@
         <v>0</v>
       </c>
       <c r="AC167" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="AD167" t="inlineStr">
         <is>
@@ -19528,12 +19528,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Kavitha Jaganathan</t>
+          <t>Maria Muhayadin</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>25953022347654371</t>
+          <t>26575694985402794</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -19556,45 +19556,45 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-03-14 17:14:06 GMT+8</t>
+          <t>2026-04-11 10:02:23 GMT+8</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>2026-03-14 17:15:34 GMT+8</t>
+          <t>2026-04-11 10:02:58 GMT+8</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-03-14 17:11:46 GMT+8</t>
+          <t>2026-04-11 10:01:46 GMT+8</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-03-14 17:11:14 GMT+8</t>
+          <t>2026-04-11 10:01:46 GMT+8</t>
         </is>
       </c>
       <c r="M168" t="n">
-        <v>12816</v>
+        <v>32596</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-03-14 17:15:34 GMT+8</t>
+          <t>2026-04-11 10:02:58 GMT+8</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Saya menyumbang 12 botol Topicana Twister kepada rumah anak yatim berhampiran rumah saya</t>
+          <t>Saya sangat suka travel bersama keluarga</t>
         </is>
       </c>
       <c r="P168" t="n">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="Q168" t="n">
-        <v>-7.8</v>
+        <v>11</v>
       </c>
       <c r="R168" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19612,7 +19612,7 @@
         <v>0</v>
       </c>
       <c r="X168" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y168" t="n">
         <v>2</v>
@@ -19643,12 +19643,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Khawlah Al Azwar</t>
+          <t>Mar Zu</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>26988101557453565</t>
+          <t>26542654198703925</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -19671,51 +19671,51 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-04-11 09:34:12 GMT+8</t>
+          <t>2026-03-30 22:22:02 GMT+8</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>2026-04-11 09:37:06 GMT+8</t>
+          <t>2026-03-30 22:22:42 GMT+8</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-04-11 09:36:16 GMT+8</t>
+          <t>2026-03-30 22:21:26 GMT+8</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-04-11 09:33:10 GMT+8</t>
+          <t>2026-03-30 22:21:25 GMT+8</t>
         </is>
       </c>
       <c r="M169" t="n">
-        <v>32535</v>
+        <v>26429</v>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-04-11 09:34:12 GMT+8</t>
+          <t>2026-03-30 22:22:02 GMT+8</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Sy suka menyeryai run harini...</t>
+          <t>Saya membantu kawan mengemas Rumah</t>
         </is>
       </c>
       <c r="P169" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q169" t="n">
-        <v>0.78</v>
+        <v>15.85</v>
       </c>
       <c r="R169" t="n">
-        <v>0.775</v>
+        <v>0.85</v>
       </c>
       <c r="S169" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T169" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U169" t="n">
         <v>0</v>
@@ -19730,10 +19730,10 @@
         <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA169" t="n">
         <v>0</v>
@@ -19758,12 +19758,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Kirtanah Ravintharan</t>
+          <t>Md</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>26327752256875020</t>
+          <t>26364307709820114</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -19786,51 +19786,51 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-04-12 09:08:22 GMT+8</t>
+          <t>2026-02-18 17:19:14 GMT+8</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>2026-04-12 09:09:16 GMT+8</t>
+          <t>2026-02-18 17:21:03 GMT+8</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-04-12 09:06:03 GMT+8</t>
+          <t>2026-02-19 17:18:14 GMT+8</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-04-12 09:06:03 GMT+8</t>
+          <t>2026-02-18 17:16:43 GMT+8</t>
         </is>
       </c>
       <c r="M170" t="n">
-        <v>33014</v>
+        <v>122</v>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-04-12 09:09:16 GMT+8</t>
+          <t>2026-02-18 17:19:14 GMT+8</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Hari ini, saya memilih untuk menyebarkan kebaikan dengan membantu jiran mengangkat barang dan berkongsi rezeki dengan rakan. Walaupun kecil, saya percaya setiap kebaikan mampu memberi makna kepada orang lain.</t>
+          <t>Menolong anak saudara membersih dan menghias rumah untuk hari persandingannya nanti Dan berkongsi Tropicana Twister bersama mereka.</t>
         </is>
       </c>
       <c r="P170" t="n">
-        <v>208</v>
+        <v>131</v>
       </c>
       <c r="Q170" t="n">
-        <v>10.2</v>
+        <v>18.27</v>
       </c>
       <c r="R170" t="n">
-        <v>5.2</v>
+        <v>3.275</v>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T170" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U170" t="n">
         <v>0</v>
@@ -19839,16 +19839,16 @@
         <v>0</v>
       </c>
       <c r="W170" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X170" t="n">
         <v>0</v>
       </c>
       <c r="Y170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA170" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>0</v>
       </c>
       <c r="AC170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD170" t="inlineStr">
         <is>
@@ -19873,12 +19873,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Lee Pei Ting</t>
+          <t>Mohamad</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>25465212196488673</t>
+          <t>25200891936250786</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -19901,35 +19901,35 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-04-11 10:00:06 GMT+8</t>
+          <t>2026-02-18 14:32:20 GMT+8</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>2026-04-11 10:00:36 GMT+8</t>
+          <t>2026-02-18 14:33:31 GMT+8</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-04-11 09:59:11 GMT+8</t>
+          <t>2026-02-18 14:30:40 GMT+8</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-04-11 09:59:11 GMT+8</t>
+          <t>2026-02-18 14:29:35 GMT+8</t>
         </is>
       </c>
       <c r="M171" t="n">
-        <v>32591</v>
+        <v>114</v>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-04-11 10:00:06 GMT+8</t>
+          <t>2026-02-18 14:32:20 GMT+8</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Say suka bersukan dengan keluarga dan kawan kawan.</t>
+          <t>saya belanja mak saya sarapan di kedai makan arini</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -19988,12 +19988,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Lukman Haqem</t>
+          <t>Mohd Hussairi</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>26297421923276894</t>
+          <t>1154988495</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -20016,54 +20016,54 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-03-15 21:32:54 GMT+8</t>
+          <t>2026-04-19 13:09:11 GMT+8</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>2026-03-15 21:33:49 GMT+8</t>
+          <t>2026-04-19 13:09:57 GMT+8</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-03-15 21:32:09 GMT+8</t>
+          <t>2026-04-19 13:08:20 GMT+8</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-03-15 21:31:38 GMT+8</t>
+          <t>2026-03-01 07:47:22 GMT+8</t>
         </is>
       </c>
       <c r="M172" t="n">
-        <v>14126</v>
+        <v>36904</v>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-03-15 21:32:54 GMT+8</t>
+          <t>2026-04-19 13:09:11 GMT+8</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Saya cuti untuk family</t>
+          <t>Setiap hari mereka datang, seolah-olah menjadi sebahagian daripada rutin hidup saya. Dari situ saya belajar tentang kasih sayang, tanggungjawab dan rasa syukur. Memberi makan kucing mungkin nampak perkara kecil, tetapi ia mengajar bahawa kebahagiaan kadang-kadang hadir melalui perbuatan yang sederhana.</t>
         </is>
       </c>
       <c r="P172" t="n">
-        <v>22</v>
+        <v>303</v>
       </c>
       <c r="Q172" t="n">
-        <v>10.55</v>
+        <v>26.58</v>
       </c>
       <c r="R172" t="n">
-        <v>0.55</v>
+        <v>7.575</v>
       </c>
       <c r="S172" t="n">
+        <v>5</v>
+      </c>
+      <c r="T172" t="n">
         <v>10</v>
       </c>
-      <c r="T172" t="n">
-        <v>0</v>
-      </c>
       <c r="U172" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V172" t="n">
         <v>0</v>
@@ -20075,13 +20075,13 @@
         <v>0</v>
       </c>
       <c r="Y172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB172" t="n">
         <v>0</v>
@@ -20103,12 +20103,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Maria Muhayadin</t>
+          <t>Mohd Khairul Hafiz</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>26575694985402794</t>
+          <t>26655419207422712</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -20131,45 +20131,45 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-04-11 10:02:23 GMT+8</t>
+          <t>2026-04-12 08:35:12 GMT+8</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>2026-04-11 10:02:58 GMT+8</t>
+          <t>2026-04-12 08:36:46 GMT+8</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-04-11 10:01:46 GMT+8</t>
+          <t>2026-04-12 08:33:41 GMT+8</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-04-11 10:01:46 GMT+8</t>
+          <t>2026-04-12 08:33:41 GMT+8</t>
         </is>
       </c>
       <c r="M173" t="n">
-        <v>32596</v>
+        <v>32901</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-04-11 10:02:58 GMT+8</t>
+          <t>2026-04-12 08:35:12 GMT+8</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Saya sangat suka travel bersama keluarga</t>
+          <t>Saya suka tropicana sebab air perisa oren dia mempunyai vitamin C dan sesuai untuk seisi keluarga</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="Q173" t="n">
-        <v>11</v>
+        <v>-7.57</v>
       </c>
       <c r="R173" t="n">
-        <v>1</v>
+        <v>2.425</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20187,7 +20187,7 @@
         <v>0</v>
       </c>
       <c r="X173" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y173" t="n">
         <v>2</v>
@@ -20218,12 +20218,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Mar Zu</t>
+          <t>Muhamad</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>26542654198703925</t>
+          <t>26808587638745229</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -20246,51 +20246,51 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2026-03-30 22:22:02 GMT+8</t>
+          <t>2026-02-20 12:44:58 GMT+8</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>2026-03-30 22:22:42 GMT+8</t>
+          <t>2026-02-20 12:48:00 GMT+8</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026-03-30 22:21:26 GMT+8</t>
+          <t>2026-02-20 12:39:36 GMT+8</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-03-30 22:21:25 GMT+8</t>
+          <t>2026-02-20 12:39:36 GMT+8</t>
         </is>
       </c>
       <c r="M174" t="n">
-        <v>26429</v>
+        <v>226</v>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-03-30 22:22:02 GMT+8</t>
+          <t>2026-02-20 12:48:00 GMT+8</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Saya membantu kawan mengemas Rumah</t>
+          <t>Sempena bulan puasa, kita boleh memperbanyakkan ibadah, bersedekah kepada yang memerlukan dan meluangkan masa bersama keluarga. Selain itu, kita juga boleh menjaga akhlak serta memperbaiki diri agar Ramadan lebih bermakna. 🌙✨</t>
         </is>
       </c>
       <c r="P174" t="n">
-        <v>34</v>
+        <v>225</v>
       </c>
       <c r="Q174" t="n">
-        <v>15.85</v>
+        <v>10.62</v>
       </c>
       <c r="R174" t="n">
-        <v>0.85</v>
+        <v>5.625</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T174" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U174" t="n">
         <v>0</v>
@@ -20305,10 +20305,10 @@
         <v>0</v>
       </c>
       <c r="Y174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA174" t="n">
         <v>0</v>
@@ -20333,12 +20333,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Md</t>
+          <t>Muhammad Zazmie Bin Amirudin</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>26364307709820114</t>
+          <t>26763040910027742</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -20361,52 +20361,52 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026-02-18 17:19:14 GMT+8</t>
+          <t>2026-04-17 15:50:53 GMT+8</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>2026-02-18 17:21:03 GMT+8</t>
+          <t>2026-04-17 16:15:11 GMT+8</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-02-19 17:18:14 GMT+8</t>
+          <t>2026-04-17 15:50:14 GMT+8</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-02-18 17:16:43 GMT+8</t>
+          <t>2026-04-17 15:50:14 GMT+8</t>
         </is>
       </c>
       <c r="M175" t="n">
-        <v>122</v>
+        <v>36526</v>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-02-18 17:19:14 GMT+8</t>
+          <t>2026-04-17 15:50:53 GMT+8</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Menolong anak saudara membersih dan menghias rumah untuk hari persandingannya nanti Dan berkongsi Tropicana Twister bersama mereka.</t>
+          <t>saya tolong tukar tayar kereta isteri</t>
         </is>
       </c>
       <c r="P175" t="n">
-        <v>131</v>
+        <v>37</v>
       </c>
       <c r="Q175" t="n">
-        <v>18.27</v>
+        <v>15.92</v>
       </c>
       <c r="R175" t="n">
-        <v>3.275</v>
+        <v>0.925</v>
       </c>
       <c r="S175" t="n">
+        <v>10</v>
+      </c>
+      <c r="T175" t="n">
         <v>5</v>
       </c>
-      <c r="T175" t="n">
-        <v>10</v>
-      </c>
       <c r="U175" t="n">
         <v>0</v>
       </c>
@@ -20420,10 +20420,10 @@
         <v>0</v>
       </c>
       <c r="Y175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA175" t="n">
         <v>0</v>
@@ -20448,12 +20448,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Mohamad</t>
+          <t>Muhd Rashid</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>25200891936250786</t>
+          <t>26335725386088254</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -20476,51 +20476,51 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2026-02-18 14:32:20 GMT+8</t>
+          <t>2026-04-17 14:07:10 GMT+8</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>2026-02-18 14:33:31 GMT+8</t>
+          <t>2026-04-17 14:09:48 GMT+8</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-02-18 14:30:40 GMT+8</t>
+          <t>2026-04-17 14:09:16 GMT+8</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-02-18 14:29:35 GMT+8</t>
+          <t>2026-04-17 14:06:02 GMT+8</t>
         </is>
       </c>
       <c r="M176" t="n">
-        <v>114</v>
+        <v>36063</v>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-02-18 14:32:20 GMT+8</t>
+          <t>2026-04-17 14:07:10 GMT+8</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>saya belanja mak saya sarapan di kedai makan arini</t>
+          <t>Saya suka membantu isteri saya dan keluarga</t>
         </is>
       </c>
       <c r="P176" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Q176" t="n">
-        <v>11.25</v>
+        <v>21.08</v>
       </c>
       <c r="R176" t="n">
-        <v>1.25</v>
+        <v>1.075</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T176" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U176" t="n">
         <v>0</v>
@@ -20535,10 +20535,10 @@
         <v>0</v>
       </c>
       <c r="Y176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA176" t="n">
         <v>0</v>
@@ -20563,12 +20563,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Mohd Hussairi</t>
+          <t>Must Leyzha</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1154988495</t>
+          <t>26109445212060830</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -20591,54 +20591,54 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-04-19 13:09:11 GMT+8</t>
+          <t>2026-04-12 09:21:24 GMT+8</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2026-04-19 13:09:57 GMT+8</t>
+          <t>2026-04-12 09:23:26 GMT+8</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026-04-19 13:08:20 GMT+8</t>
+          <t>2026-04-12 09:19:10 GMT+8</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-03-01 07:47:22 GMT+8</t>
+          <t>2026-04-12 09:19:10 GMT+8</t>
         </is>
       </c>
       <c r="M177" t="n">
-        <v>36904</v>
+        <v>33058</v>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-04-19 13:09:11 GMT+8</t>
+          <t>2026-04-12 09:21:24 GMT+8</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Setiap hari mereka datang, seolah-olah menjadi sebahagian daripada rutin hidup saya. Dari situ saya belajar tentang kasih sayang, tanggungjawab dan rasa syukur. Memberi makan kucing mungkin nampak perkara kecil, tetapi ia mengajar bahawa kebahagiaan kadang-kadang hadir melalui perbuatan yang sederhana.</t>
+          <t>Saya kongsikan Tropicana Twister bersama rakan untuk sebarkan keenakan rasa dari setiap tegukan.</t>
         </is>
       </c>
       <c r="P177" t="n">
-        <v>303</v>
+        <v>96</v>
       </c>
       <c r="Q177" t="n">
-        <v>26.58</v>
+        <v>-7.6</v>
       </c>
       <c r="R177" t="n">
-        <v>7.575</v>
+        <v>2.4</v>
       </c>
       <c r="S177" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T177" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U177" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V177" t="n">
         <v>0</v>
@@ -20647,16 +20647,16 @@
         <v>0</v>
       </c>
       <c r="X177" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB177" t="n">
         <v>0</v>
@@ -20678,12 +20678,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Mohd Khairul Hafiz</t>
+          <t>Nazatul Farhanis</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>26655419207422712</t>
+          <t>26556939267307727</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -20706,51 +20706,51 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-04-12 08:35:12 GMT+8</t>
+          <t>2026-04-17 16:43:36 GMT+8</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>2026-04-12 08:36:46 GMT+8</t>
+          <t>2026-04-17 17:42:09 GMT+8</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026-04-12 08:33:41 GMT+8</t>
+          <t>2026-04-17 16:41:49 GMT+8</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-04-12 08:33:41 GMT+8</t>
+          <t>2026-04-17 16:41:49 GMT+8</t>
         </is>
       </c>
       <c r="M178" t="n">
-        <v>32901</v>
+        <v>36765</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-04-12 08:35:12 GMT+8</t>
+          <t>2026-04-17 17:42:09 GMT+8</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>Saya suka tropicana sebab air perisa oren dia mempunyai vitamin C dan sesuai untuk seisi keluarga</t>
+          <t>saya suka berkongsi tropicana twister bersamaa family</t>
         </is>
       </c>
       <c r="P178" t="n">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="Q178" t="n">
-        <v>-7.57</v>
+        <v>-3.68</v>
       </c>
       <c r="R178" t="n">
-        <v>2.425</v>
+        <v>1.325</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
       </c>
       <c r="T178" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U178" t="n">
         <v>0</v>
@@ -20768,7 +20768,7 @@
         <v>2</v>
       </c>
       <c r="Z178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA178" t="n">
         <v>0</v>
@@ -20793,12 +20793,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Muhamad</t>
+          <t>Nazihah Shukor</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>26808587638745229</t>
+          <t>34216781017966905</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -20821,52 +20821,52 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-02-20 12:44:58 GMT+8</t>
+          <t>2026-03-15 18:48:58 GMT+8</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>2026-02-20 12:48:00 GMT+8</t>
+          <t>2026-03-15 18:50:41 GMT+8</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026-02-20 12:39:36 GMT+8</t>
+          <t>2026-03-15 18:28:53 GMT+8</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-02-20 12:39:36 GMT+8</t>
+          <t>2026-03-15 15:40:08 GMT+8</t>
         </is>
       </c>
       <c r="M179" t="n">
-        <v>226</v>
+        <v>13784</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-02-20 12:48:00 GMT+8</t>
+          <t>2026-03-15 18:50:41 GMT+8</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Sempena bulan puasa, kita boleh memperbanyakkan ibadah, bersedekah kepada yang memerlukan dan meluangkan masa bersama keluarga. Selain itu, kita juga boleh menjaga akhlak serta memperbaiki diri agar Ramadan lebih bermakna. 🌙✨</t>
+          <t>Saya bantu ibu di dapur</t>
         </is>
       </c>
       <c r="P179" t="n">
-        <v>225</v>
+        <v>23</v>
       </c>
       <c r="Q179" t="n">
-        <v>10.62</v>
+        <v>15.58</v>
       </c>
       <c r="R179" t="n">
-        <v>5.625</v>
+        <v>0.575</v>
       </c>
       <c r="S179" t="n">
+        <v>10</v>
+      </c>
+      <c r="T179" t="n">
         <v>5</v>
       </c>
-      <c r="T179" t="n">
-        <v>0</v>
-      </c>
       <c r="U179" t="n">
         <v>0</v>
       </c>
@@ -20880,10 +20880,10 @@
         <v>0</v>
       </c>
       <c r="Y179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA179" t="n">
         <v>0</v>
@@ -20908,12 +20908,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Muhammad Zazmie Bin Amirudin</t>
+          <t>Ng</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>26763040910027742</t>
+          <t>51023365</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -20936,51 +20936,51 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-04-17 15:50:53 GMT+8</t>
+          <t>2026-02-23 00:35:29 GMT+8</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>2026-04-17 16:15:11 GMT+8</t>
+          <t>2026-02-23 00:36:11 GMT+8</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026-04-17 15:50:14 GMT+8</t>
+          <t>2026-02-23 00:26:47 GMT+8</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-04-17 15:50:14 GMT+8</t>
+          <t>2026-02-18 19:51:32 GMT+8</t>
         </is>
       </c>
       <c r="M180" t="n">
-        <v>36526</v>
+        <v>498</v>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-04-17 15:50:53 GMT+8</t>
+          <t>2026-02-23 00:35:29 GMT+8</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>saya tolong tukar tayar kereta isteri</t>
+          <t>Saya mengucapkan gong xi fa chai dengan jiran lain kaum sempena tahun Baru Cina</t>
         </is>
       </c>
       <c r="P180" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="Q180" t="n">
-        <v>15.92</v>
+        <v>11.98</v>
       </c>
       <c r="R180" t="n">
-        <v>0.925</v>
+        <v>1.975</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
       </c>
       <c r="T180" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U180" t="n">
         <v>0</v>
@@ -20998,7 +20998,7 @@
         <v>2</v>
       </c>
       <c r="Z180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA180" t="n">
         <v>0</v>
@@ -21023,12 +21023,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Muhd Rashid</t>
+          <t>Nisya MK</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>26335725386088254</t>
+          <t>27418689047734291</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -21051,48 +21051,48 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-04-17 14:07:10 GMT+8</t>
+          <t>2026-04-17 16:22:14 GMT+8</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>2026-04-17 14:09:48 GMT+8</t>
+          <t>2026-04-17 16:51:58 GMT+8</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-04-17 14:09:16 GMT+8</t>
+          <t>2026-04-17 16:51:08 GMT+8</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-04-17 14:06:02 GMT+8</t>
+          <t>2026-04-17 16:21:17 GMT+8</t>
         </is>
       </c>
       <c r="M181" t="n">
-        <v>36063</v>
+        <v>36675</v>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-04-17 14:07:10 GMT+8</t>
+          <t>2026-04-17 16:51:58 GMT+8</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>Saya suka membantu isteri saya dan keluarga</t>
+          <t>Kongsi makanan bersama kawan</t>
         </is>
       </c>
       <c r="P181" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="Q181" t="n">
-        <v>21.08</v>
+        <v>10.7</v>
       </c>
       <c r="R181" t="n">
-        <v>1.075</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="S181" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T181" t="n">
         <v>5</v>
@@ -21110,7 +21110,7 @@
         <v>0</v>
       </c>
       <c r="Y181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z181" t="n">
         <v>1</v>
@@ -21138,12 +21138,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Must Leyzha</t>
+          <t>Noor Izzati Binti Harun</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>26109445212060830</t>
+          <t>26430716853250252</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -21166,45 +21166,45 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2026-04-12 09:21:24 GMT+8</t>
+          <t>2026-04-12 08:12:59 GMT+8</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>2026-04-12 09:23:26 GMT+8</t>
+          <t>2026-04-12 08:14:34 GMT+8</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026-04-12 09:19:10 GMT+8</t>
+          <t>2026-04-12 08:10:40 GMT+8</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-04-12 09:19:10 GMT+8</t>
+          <t>2026-04-12 08:10:01 GMT+8</t>
         </is>
       </c>
       <c r="M182" t="n">
-        <v>33058</v>
+        <v>32841</v>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-04-12 09:21:24 GMT+8</t>
+          <t>2026-04-12 08:14:34 GMT+8</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>Saya kongsikan Tropicana Twister bersama rakan untuk sebarkan keenakan rasa dari setiap tegukan.</t>
+          <t>Saya menderma dan sertai program pendidikan untuk anak orang asli</t>
         </is>
       </c>
       <c r="P182" t="n">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="Q182" t="n">
-        <v>-7.6</v>
+        <v>11.62</v>
       </c>
       <c r="R182" t="n">
-        <v>2.4</v>
+        <v>1.625</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21222,7 +21222,7 @@
         <v>0</v>
       </c>
       <c r="X182" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y182" t="n">
         <v>2</v>
@@ -21253,12 +21253,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Nazatul Farhanis</t>
+          <t>Noor Shahirah Othman</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>26556939267307727</t>
+          <t>26191985463784477</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -21281,51 +21281,51 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2026-04-17 16:43:36 GMT+8</t>
+          <t>2026-03-14 11:09:25 GMT+8</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>2026-04-17 17:42:09 GMT+8</t>
+          <t>2026-03-14 11:10:33 GMT+8</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026-04-17 16:41:49 GMT+8</t>
+          <t>2026-03-14 11:07:40 GMT+8</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-04-17 16:41:49 GMT+8</t>
+          <t>2026-03-14 11:07:40 GMT+8</t>
         </is>
       </c>
       <c r="M183" t="n">
-        <v>36765</v>
+        <v>12614</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-04-17 17:42:09 GMT+8</t>
+          <t>2026-03-14 11:10:33 GMT+8</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>saya suka berkongsi tropicana twister bersamaa family</t>
+          <t>Saya bawa kucing sakit ke klinik</t>
         </is>
       </c>
       <c r="P183" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="Q183" t="n">
-        <v>-3.68</v>
+        <v>5.8</v>
       </c>
       <c r="R183" t="n">
-        <v>1.325</v>
+        <v>0.8</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T183" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U183" t="n">
         <v>0</v>
@@ -21337,13 +21337,13 @@
         <v>0</v>
       </c>
       <c r="X183" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA183" t="n">
         <v>0</v>
@@ -21368,12 +21368,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Nazihah Shukor</t>
+          <t>Nuraina Shahirah</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>34216781017966905</t>
+          <t>26102771442752311</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -21396,51 +21396,51 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-03-15 18:48:58 GMT+8</t>
+          <t>2026-04-12 08:14:27 GMT+8</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>2026-03-15 18:50:41 GMT+8</t>
+          <t>2026-04-12 08:17:32 GMT+8</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:53 GMT+8</t>
+          <t>2026-04-12 08:12:27 GMT+8</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-03-15 15:40:08 GMT+8</t>
+          <t>2026-04-12 08:12:26 GMT+8</t>
         </is>
       </c>
       <c r="M184" t="n">
-        <v>13784</v>
+        <v>32839</v>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-03-15 18:50:41 GMT+8</t>
+          <t>2026-04-12 08:14:27 GMT+8</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>Saya bantu ibu di dapur</t>
+          <t>saya sering membantu keluarga untuk kebaikan</t>
         </is>
       </c>
       <c r="P184" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="Q184" t="n">
-        <v>15.58</v>
+        <v>21.1</v>
       </c>
       <c r="R184" t="n">
-        <v>0.575</v>
+        <v>1.1</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
       </c>
       <c r="T184" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U184" t="n">
         <v>0</v>
@@ -21458,7 +21458,7 @@
         <v>2</v>
       </c>
       <c r="Z184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA184" t="n">
         <v>0</v>
@@ -21483,12 +21483,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Nur Aqilah</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>51023365</t>
+          <t>35914641104802071</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -21511,51 +21511,51 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-02-23 00:35:29 GMT+8</t>
+          <t>2026-04-12 08:55:01 GMT+8</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>2026-02-23 00:36:11 GMT+8</t>
+          <t>2026-04-12 08:57:32 GMT+8</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026-02-23 00:26:47 GMT+8</t>
+          <t>2026-04-12 08:53:55 GMT+8</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-02-18 19:51:32 GMT+8</t>
+          <t>2026-04-12 08:53:54 GMT+8</t>
         </is>
       </c>
       <c r="M185" t="n">
-        <v>498</v>
+        <v>32975</v>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-02-23 00:35:29 GMT+8</t>
+          <t>2026-04-12 08:57:32 GMT+8</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>Saya mengucapkan gong xi fa chai dengan jiran lain kaum sempena tahun Baru Cina</t>
+          <t>Saya suka bantu ibu bapak membuat kerja rumah.</t>
         </is>
       </c>
       <c r="P185" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="Q185" t="n">
-        <v>11.98</v>
+        <v>16.15</v>
       </c>
       <c r="R185" t="n">
-        <v>1.975</v>
+        <v>1.15</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
       </c>
       <c r="T185" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U185" t="n">
         <v>0</v>
@@ -21573,7 +21573,7 @@
         <v>2</v>
       </c>
       <c r="Z185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA185" t="n">
         <v>0</v>
@@ -21598,12 +21598,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Nisya MK</t>
+          <t>Nur Kiawati Wahib</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>27418689047734291</t>
+          <t>26623628940658692</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -21626,45 +21626,45 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-04-17 16:22:14 GMT+8</t>
+          <t>2026-04-11 08:07:22 GMT+8</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>2026-04-17 16:51:58 GMT+8</t>
+          <t>2026-04-11 08:09:13 GMT+8</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026-04-17 16:51:08 GMT+8</t>
+          <t>2026-04-11 08:05:06 GMT+8</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-04-17 16:21:17 GMT+8</t>
+          <t>2026-04-11 08:04:33 GMT+8</t>
         </is>
       </c>
       <c r="M186" t="n">
-        <v>36675</v>
+        <v>32416</v>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-04-17 16:51:58 GMT+8</t>
+          <t>2026-04-11 08:09:13 GMT+8</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Kongsi makanan bersama kawan</t>
+          <t>Saya suka masak dan kongsi dengan rakan2</t>
         </is>
       </c>
       <c r="P186" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q186" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="R186" t="n">
-        <v>0.7000000000000001</v>
+        <v>1</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -21713,12 +21713,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Noor Izzati Binti Harun</t>
+          <t>Nurnadia Kamaruzzaman</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>26430716853250252</t>
+          <t>26692733340416745</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -21741,51 +21741,51 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-04-12 08:12:59 GMT+8</t>
+          <t>2026-04-17 15:05:53 GMT+8</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>2026-04-12 08:14:34 GMT+8</t>
+          <t>2026-04-17 16:39:53 GMT+8</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2026-04-12 08:10:40 GMT+8</t>
+          <t>2026-04-17 15:04:40 GMT+8</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-04-12 08:10:01 GMT+8</t>
+          <t>2026-04-17 15:04:39 GMT+8</t>
         </is>
       </c>
       <c r="M187" t="n">
-        <v>32841</v>
+        <v>36648</v>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-04-12 08:14:34 GMT+8</t>
+          <t>2026-04-17 16:39:53 GMT+8</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>Saya menderma dan sertai program pendidikan untuk anak orang asli</t>
+          <t>Saya suka tolong mak saya buat kerja rumah.</t>
         </is>
       </c>
       <c r="P187" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="Q187" t="n">
-        <v>11.62</v>
+        <v>16.08</v>
       </c>
       <c r="R187" t="n">
-        <v>1.625</v>
+        <v>1.075</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
       </c>
       <c r="T187" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U187" t="n">
         <v>0</v>
@@ -21803,7 +21803,7 @@
         <v>2</v>
       </c>
       <c r="Z187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA187" t="n">
         <v>0</v>
@@ -21828,12 +21828,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Noor Shahirah Othman</t>
+          <t>Nurul Akma Ma</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>26191985463784477</t>
+          <t>640052213</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -21856,52 +21856,52 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-03-14 11:09:25 GMT+8</t>
+          <t>2026-04-04 16:28:10 GMT+8</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>2026-03-14 11:10:33 GMT+8</t>
+          <t>2026-04-04 16:30:46 GMT+8</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026-03-14 11:07:40 GMT+8</t>
+          <t>2026-04-04 16:29:39 GMT+8</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-03-14 11:07:40 GMT+8</t>
+          <t>2026-02-16 12:30:19 GMT+8</t>
         </is>
       </c>
       <c r="M188" t="n">
-        <v>12614</v>
+        <v>29990</v>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-03-14 11:10:33 GMT+8</t>
+          <t>2026-04-04 16:28:10 GMT+8</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>Saya bawa kucing sakit ke klinik</t>
+          <t>Saya bantu jiran menyiram bunga setiap kali dia pergi bercuti</t>
         </is>
       </c>
       <c r="P188" t="n">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="Q188" t="n">
-        <v>5.8</v>
+        <v>16.52</v>
       </c>
       <c r="R188" t="n">
-        <v>0.8</v>
+        <v>1.525</v>
       </c>
       <c r="S188" t="n">
+        <v>10</v>
+      </c>
+      <c r="T188" t="n">
         <v>5</v>
       </c>
-      <c r="T188" t="n">
-        <v>0</v>
-      </c>
       <c r="U188" t="n">
         <v>0</v>
       </c>
@@ -21915,10 +21915,10 @@
         <v>0</v>
       </c>
       <c r="Y188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA188" t="n">
         <v>0</v>
@@ -21943,12 +21943,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Nuraina Shahirah</t>
+          <t>Nurul Izzah</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>26102771442752311</t>
+          <t>26645250761779875</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -21971,57 +21971,57 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-04-12 08:14:27 GMT+8</t>
+          <t>2026-04-12 08:14:06 GMT+8</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>2026-04-12 08:17:32 GMT+8</t>
+          <t>2026-04-12 08:17:24 GMT+8</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026-04-12 08:12:27 GMT+8</t>
+          <t>2026-04-12 08:12:41 GMT+8</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-04-12 08:12:26 GMT+8</t>
+          <t>2026-04-12 08:12:41 GMT+8</t>
         </is>
       </c>
       <c r="M189" t="n">
-        <v>32839</v>
+        <v>32849</v>
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-04-12 08:14:27 GMT+8</t>
+          <t>2026-04-12 08:17:24 GMT+8</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>saya sering membantu keluarga untuk kebaikan</t>
+          <t>saya sering membantu ibu bapa ketika masa lapang.</t>
         </is>
       </c>
       <c r="P189" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Q189" t="n">
-        <v>21.1</v>
+        <v>25.22</v>
       </c>
       <c r="R189" t="n">
-        <v>1.1</v>
+        <v>1.225</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T189" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U189" t="n">
         <v>0</v>
       </c>
       <c r="V189" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W189" t="n">
         <v>0</v>
@@ -22030,16 +22030,16 @@
         <v>0</v>
       </c>
       <c r="Y189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA189" t="n">
         <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC189" t="n">
         <v>1</v>
@@ -22058,12 +22058,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Nur Aqilah</t>
+          <t>Nurul Knewrul</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>35914641104802071</t>
+          <t>35133283479620209</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -22086,51 +22086,51 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-04-12 08:55:01 GMT+8</t>
+          <t>2026-04-11 08:07:30 GMT+8</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>2026-04-12 08:57:32 GMT+8</t>
+          <t>2026-04-11 08:08:39 GMT+8</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026-04-12 08:53:55 GMT+8</t>
+          <t>2026-04-11 08:04:20 GMT+8</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-04-12 08:53:54 GMT+8</t>
+          <t>2026-04-11 08:03:47 GMT+8</t>
         </is>
       </c>
       <c r="M190" t="n">
-        <v>32975</v>
+        <v>32412</v>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-04-12 08:57:32 GMT+8</t>
+          <t>2026-04-11 08:08:39 GMT+8</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Saya suka bantu ibu bapak membuat kerja rumah.</t>
+          <t>Saya suka jalan jalan bawa family jalan</t>
         </is>
       </c>
       <c r="P190" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q190" t="n">
-        <v>16.15</v>
+        <v>10.98</v>
       </c>
       <c r="R190" t="n">
-        <v>1.15</v>
+        <v>0.9750000000000001</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
       </c>
       <c r="T190" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U190" t="n">
         <v>0</v>
@@ -22148,7 +22148,7 @@
         <v>2</v>
       </c>
       <c r="Z190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA190" t="n">
         <v>0</v>
@@ -22173,12 +22173,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Nur Kiawati Wahib</t>
+          <t>Nurul Syafiqa</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>26623628940658692</t>
+          <t>26307608435574839</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -22201,51 +22201,51 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2026-04-11 08:07:22 GMT+8</t>
+          <t>2026-04-17 16:25:12 GMT+8</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>2026-04-11 08:09:13 GMT+8</t>
+          <t>2026-04-17 16:48:29 GMT+8</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2026-04-11 08:05:06 GMT+8</t>
+          <t>2026-04-17 16:47:44 GMT+8</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-04-11 08:04:33 GMT+8</t>
+          <t>2026-04-17 16:24:27 GMT+8</t>
         </is>
       </c>
       <c r="M191" t="n">
-        <v>32416</v>
+        <v>36615</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-04-11 08:09:13 GMT+8</t>
+          <t>2026-04-17 16:25:12 GMT+8</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>Saya suka masak dan kongsi dengan rakan2</t>
+          <t>Saya bantu kawan untuk membeli dan berkongsi air twister</t>
         </is>
       </c>
       <c r="P191" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="Q191" t="n">
-        <v>11</v>
+        <v>1.4</v>
       </c>
       <c r="R191" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T191" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U191" t="n">
         <v>0</v>
@@ -22257,13 +22257,13 @@
         <v>0</v>
       </c>
       <c r="X191" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA191" t="n">
         <v>0</v>
@@ -22288,12 +22288,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Nurnadia Kamaruzzaman</t>
+          <t>Nurzilawati Hussin</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>26692733340416745</t>
+          <t>2171357792955214</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -22316,54 +22316,54 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-04-17 15:05:53 GMT+8</t>
+          <t>2026-04-11 08:05:26 GMT+8</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>2026-04-17 16:39:53 GMT+8</t>
+          <t>2026-04-11 08:06:31 GMT+8</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2026-04-17 15:04:40 GMT+8</t>
+          <t>2026-04-11 08:02:57 GMT+8</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-04-17 15:04:39 GMT+8</t>
+          <t>2026-04-11 08:00:41 GMT+8</t>
         </is>
       </c>
       <c r="M192" t="n">
-        <v>36648</v>
+        <v>32400</v>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-04-17 16:39:53 GMT+8</t>
+          <t>2026-04-11 08:05:26 GMT+8</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Saya suka tolong mak saya buat kerja rumah.</t>
+          <t>Bersama twister hidup pasti gembira</t>
         </is>
       </c>
       <c r="P192" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="Q192" t="n">
-        <v>16.08</v>
+        <v>-10.12</v>
       </c>
       <c r="R192" t="n">
-        <v>1.075</v>
+        <v>0.875</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T192" t="n">
         <v>5</v>
       </c>
       <c r="U192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V192" t="n">
         <v>0</v>
@@ -22372,16 +22372,16 @@
         <v>0</v>
       </c>
       <c r="X192" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z192" t="n">
         <v>1</v>
       </c>
       <c r="AA192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB192" t="n">
         <v>0</v>
@@ -22403,12 +22403,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Nurul Akma Ma</t>
+          <t>Rasidah Rosmanan</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>640052213</t>
+          <t>35023451573969923</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -22431,45 +22431,45 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-04-04 16:28:10 GMT+8</t>
+          <t>2026-04-17 15:44:23 GMT+8</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>2026-04-04 16:30:46 GMT+8</t>
+          <t>2026-04-17 16:11:53 GMT+8</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2026-04-04 16:29:39 GMT+8</t>
+          <t>2026-04-17 16:11:11 GMT+8</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-02-16 12:30:19 GMT+8</t>
+          <t>2026-04-17 15:43:35 GMT+8</t>
         </is>
       </c>
       <c r="M193" t="n">
-        <v>29990</v>
+        <v>36581</v>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-04-04 16:28:10 GMT+8</t>
+          <t>2026-04-17 16:11:53 GMT+8</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Saya bantu jiran menyiram bunga setiap kali dia pergi bercuti</t>
+          <t>Saya suka bantu keluarga saya</t>
         </is>
       </c>
       <c r="P193" t="n">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="Q193" t="n">
-        <v>16.52</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="R193" t="n">
-        <v>1.525</v>
+        <v>0.725</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22484,7 +22484,7 @@
         <v>0</v>
       </c>
       <c r="W193" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="X193" t="n">
         <v>0</v>
@@ -22502,7 +22502,7 @@
         <v>0</v>
       </c>
       <c r="AC193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD193" t="inlineStr">
         <is>
@@ -22518,12 +22518,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Nurul Izzah</t>
+          <t>Saiful Haizam</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>26645250761779875</t>
+          <t>537089163</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -22546,48 +22546,48 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-04-12 08:14:06 GMT+8</t>
+          <t>2026-03-16 23:30:39 GMT+8</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>2026-04-12 08:17:24 GMT+8</t>
+          <t>2026-03-16 23:34:04 GMT+8</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2026-04-12 08:12:41 GMT+8</t>
+          <t>2026-03-16 23:24:24 GMT+8</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-04-12 08:12:41 GMT+8</t>
+          <t>2026-02-20 22:23:49 GMT+8</t>
         </is>
       </c>
       <c r="M194" t="n">
-        <v>32849</v>
+        <v>15579</v>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-04-12 08:17:24 GMT+8</t>
+          <t>2026-03-16 23:30:39 GMT+8</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>saya sering membantu ibu bapa ketika masa lapang.</t>
+          <t>Saya berkongsi rezeki dengan membeli Tropicana Twister dan kemudian diagih-agihkan kepada jiran tetangga</t>
         </is>
       </c>
       <c r="P194" t="n">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="Q194" t="n">
-        <v>25.22</v>
+        <v>-2.4</v>
       </c>
       <c r="R194" t="n">
-        <v>1.225</v>
+        <v>2.6</v>
       </c>
       <c r="S194" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T194" t="n">
         <v>5</v>
@@ -22596,16 +22596,16 @@
         <v>0</v>
       </c>
       <c r="V194" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W194" t="n">
         <v>0</v>
       </c>
       <c r="X194" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y194" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z194" t="n">
         <v>1</v>
@@ -22614,7 +22614,7 @@
         <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC194" t="n">
         <v>1</v>
@@ -22633,12 +22633,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Nurul Knewrul</t>
+          <t>Salmah Jaafar</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>35133283479620209</t>
+          <t>26750312877989179</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -22661,51 +22661,51 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-04-11 08:07:30 GMT+8</t>
+          <t>2026-04-12 09:42:11 GMT+8</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>2026-04-11 08:08:39 GMT+8</t>
+          <t>2026-04-12 09:43:52 GMT+8</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026-04-11 08:04:20 GMT+8</t>
+          <t>2026-04-12 09:40:28 GMT+8</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-04-11 08:03:47 GMT+8</t>
+          <t>2026-04-12 09:40:28 GMT+8</t>
         </is>
       </c>
       <c r="M195" t="n">
-        <v>32412</v>
+        <v>33096</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-04-11 08:08:39 GMT+8</t>
+          <t>2026-04-12 09:43:52 GMT+8</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Saya suka jalan jalan bawa family jalan</t>
+          <t>Saya bantu orang menunjukan jalan.</t>
         </is>
       </c>
       <c r="P195" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="Q195" t="n">
-        <v>10.98</v>
+        <v>10.85</v>
       </c>
       <c r="R195" t="n">
-        <v>0.9750000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T195" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U195" t="n">
         <v>0</v>
@@ -22720,10 +22720,10 @@
         <v>0</v>
       </c>
       <c r="Y195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA195" t="n">
         <v>0</v>
@@ -22748,12 +22748,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Nurul Syafiqa</t>
+          <t>Sariffudin Fiza</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>26307608435574839</t>
+          <t>25640455475627828</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -22776,51 +22776,51 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-04-17 16:25:12 GMT+8</t>
+          <t>2026-04-17 15:40:28 GMT+8</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>2026-04-17 16:48:29 GMT+8</t>
+          <t>2026-04-17 16:13:56 GMT+8</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026-04-17 16:47:44 GMT+8</t>
+          <t>2026-04-17 16:12:47 GMT+8</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-04-17 16:24:27 GMT+8</t>
+          <t>2026-04-17 15:39:37 GMT+8</t>
         </is>
       </c>
       <c r="M196" t="n">
-        <v>36615</v>
+        <v>36502</v>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-04-17 16:25:12 GMT+8</t>
+          <t>2026-04-17 15:40:28 GMT+8</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>Saya bantu kawan untuk membeli dan berkongsi air twister</t>
+          <t>saya sayang family saya</t>
         </is>
       </c>
       <c r="P196" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="Q196" t="n">
-        <v>1.4</v>
+        <v>-9.43</v>
       </c>
       <c r="R196" t="n">
-        <v>1.4</v>
+        <v>0.575</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
       </c>
       <c r="T196" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U196" t="n">
         <v>0</v>
@@ -22829,16 +22829,16 @@
         <v>0</v>
       </c>
       <c r="W196" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="X196" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y196" t="n">
         <v>2</v>
       </c>
       <c r="Z196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA196" t="n">
         <v>0</v>
@@ -22847,7 +22847,7 @@
         <v>0</v>
       </c>
       <c r="AC196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD196" t="inlineStr">
         <is>
@@ -22863,12 +22863,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Nurzilawati Hussin</t>
+          <t>Shameel Isfahan</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2171357792955214</t>
+          <t>25409058178770177</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -22891,54 +22891,54 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-04-11 08:05:26 GMT+8</t>
+          <t>2026-04-12 09:57:57 GMT+8</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>2026-04-11 08:06:31 GMT+8</t>
+          <t>2026-04-12 10:26:46 GMT+8</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026-04-11 08:02:57 GMT+8</t>
+          <t>2026-04-12 09:56:09 GMT+8</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-04-11 08:00:41 GMT+8</t>
+          <t>2026-04-12 09:56:08 GMT+8</t>
         </is>
       </c>
       <c r="M197" t="n">
-        <v>32400</v>
+        <v>33118</v>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-04-11 08:05:26 GMT+8</t>
+          <t>2026-04-12 09:57:57 GMT+8</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>Bersama twister hidup pasti gembira</t>
+          <t>Saya suka berlari sambil bersedekah</t>
         </is>
       </c>
       <c r="P197" t="n">
         <v>35</v>
       </c>
       <c r="Q197" t="n">
-        <v>-10.12</v>
+        <v>5.88</v>
       </c>
       <c r="R197" t="n">
         <v>0.875</v>
       </c>
       <c r="S197" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T197" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U197" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V197" t="n">
         <v>0</v>
@@ -22947,16 +22947,16 @@
         <v>0</v>
       </c>
       <c r="X197" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB197" t="n">
         <v>0</v>
@@ -22978,12 +22978,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Rasidah Rosmanan</t>
+          <t>Shazlin Rosly</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>35023451573969923</t>
+          <t>26809398435345201</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -23006,45 +23006,45 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-04-17 15:44:23 GMT+8</t>
+          <t>2026-04-12 08:22:19 GMT+8</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>2026-04-17 16:11:53 GMT+8</t>
+          <t>2026-04-12 08:22:53 GMT+8</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-04-17 16:11:11 GMT+8</t>
+          <t>2026-04-12 08:20:50 GMT+8</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-04-17 15:43:35 GMT+8</t>
+          <t>2026-04-12 08:20:49 GMT+8</t>
         </is>
       </c>
       <c r="M198" t="n">
-        <v>36581</v>
+        <v>32871</v>
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-04-17 16:11:53 GMT+8</t>
+          <t>2026-04-12 08:22:53 GMT+8</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>Saya suka bantu keluarga saya</t>
+          <t>Saya Bantu jiran angkat air</t>
         </is>
       </c>
       <c r="P198" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q198" t="n">
-        <v>-9.279999999999999</v>
+        <v>15.68</v>
       </c>
       <c r="R198" t="n">
-        <v>0.725</v>
+        <v>0.6749999999999999</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -23059,7 +23059,7 @@
         <v>0</v>
       </c>
       <c r="W198" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X198" t="n">
         <v>0</v>
@@ -23077,7 +23077,7 @@
         <v>0</v>
       </c>
       <c r="AC198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD198" t="inlineStr">
         <is>
@@ -23093,12 +23093,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Saiful Haizam</t>
+          <t>Shera Nazri</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>537089163</t>
+          <t>187412901</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -23121,45 +23121,45 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-03-16 23:30:39 GMT+8</t>
+          <t>2026-03-16 05:58:14 GMT+8</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>2026-03-16 23:34:04 GMT+8</t>
+          <t>2026-03-16 05:58:47 GMT+8</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026-03-16 23:24:24 GMT+8</t>
+          <t>2026-04-03 13:41:35 GMT+8</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-02-20 22:23:49 GMT+8</t>
+          <t>2026-03-16 05:56:01 GMT+8</t>
         </is>
       </c>
       <c r="M199" t="n">
-        <v>15579</v>
+        <v>14177</v>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-03-16 23:30:39 GMT+8</t>
+          <t>2026-03-16 05:58:47 GMT+8</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>Saya berkongsi rezeki dengan membeli Tropicana Twister dan kemudian diagih-agihkan kepada jiran tetangga</t>
+          <t>Saya bantu keluarga saya mengecat rumah</t>
         </is>
       </c>
       <c r="P199" t="n">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="Q199" t="n">
-        <v>-2.4</v>
+        <v>15.98</v>
       </c>
       <c r="R199" t="n">
-        <v>2.6</v>
+        <v>0.9750000000000001</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -23177,7 +23177,7 @@
         <v>0</v>
       </c>
       <c r="X199" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y199" t="n">
         <v>2</v>
@@ -23208,12 +23208,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Salmah Jaafar</t>
+          <t>Shira Jalil</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>26750312877989179</t>
+          <t>26304478562497060</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -23236,45 +23236,45 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-04-12 09:42:11 GMT+8</t>
+          <t>2026-03-14 01:22:42 GMT+8</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>2026-04-12 09:43:52 GMT+8</t>
+          <t>2026-03-14 01:24:53 GMT+8</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-04-12 09:40:28 GMT+8</t>
+          <t>2026-03-14 01:24:08 GMT+8</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-04-12 09:40:28 GMT+8</t>
+          <t>2026-03-14 01:21:38 GMT+8</t>
         </is>
       </c>
       <c r="M200" t="n">
-        <v>33096</v>
+        <v>11836</v>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-04-12 09:43:52 GMT+8</t>
+          <t>2026-03-14 01:24:53 GMT+8</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Saya bantu orang menunjukan jalan.</t>
+          <t>saya suka tolong orang</t>
         </is>
       </c>
       <c r="P200" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="Q200" t="n">
-        <v>10.85</v>
+        <v>-14.45</v>
       </c>
       <c r="R200" t="n">
-        <v>0.85</v>
+        <v>0.55</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -23289,7 +23289,7 @@
         <v>0</v>
       </c>
       <c r="W200" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="X200" t="n">
         <v>0</v>
@@ -23307,7 +23307,7 @@
         <v>0</v>
       </c>
       <c r="AC200" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AD200" t="inlineStr">
         <is>
@@ -23323,12 +23323,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Sariffudin Fiza</t>
+          <t>Siew</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>25640455475627828</t>
+          <t>765882994</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -23351,51 +23351,51 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-04-17 15:40:28 GMT+8</t>
+          <t>2026-02-20 12:39:13 GMT+8</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>2026-04-17 16:13:56 GMT+8</t>
+          <t>2026-02-20 12:41:25 GMT+8</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026-04-17 16:12:47 GMT+8</t>
+          <t>2026-02-20 12:34:32 GMT+8</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-04-17 15:39:37 GMT+8</t>
+          <t>2026-02-20 12:33:49 GMT+8</t>
         </is>
       </c>
       <c r="M201" t="n">
-        <v>36502</v>
+        <v>220</v>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-04-17 15:40:28 GMT+8</t>
+          <t>2026-02-20 12:39:13 GMT+8</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>saya sayang family saya</t>
+          <t>Saya memperkenalkan minuman tropicana Twister kepada kawan sekerja saya. Selain itu, Tropicana Twister merupakan minuman utama tajaan saya kepada jamuan di anak sekolah saya.</t>
         </is>
       </c>
       <c r="P201" t="n">
-        <v>23</v>
+        <v>174</v>
       </c>
       <c r="Q201" t="n">
-        <v>-9.43</v>
+        <v>19.35</v>
       </c>
       <c r="R201" t="n">
-        <v>0.575</v>
+        <v>4.35</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T201" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U201" t="n">
         <v>0</v>
@@ -23404,16 +23404,16 @@
         <v>0</v>
       </c>
       <c r="W201" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X201" t="n">
         <v>0</v>
       </c>
       <c r="Y201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA201" t="n">
         <v>0</v>
@@ -23422,7 +23422,7 @@
         <v>0</v>
       </c>
       <c r="AC201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD201" t="inlineStr">
         <is>
